--- a/templates/BNYCL12879 - template.xlsx
+++ b/templates/BNYCL12879 - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1391,96 +1391,96 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B18" s="36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
-        <v>1.10196419</v>
+        <v>1.10889283</v>
       </c>
       <c r="D18" s="38" t="n">
-        <v>0.0004331507910195764</v>
+        <v>0.001739228925552228</v>
       </c>
       <c r="E18" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="39" t="n">
-        <v>0.7981957531221319</v>
+        <v>3.204992743555244</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="41" t="n">
-        <v>1.10148708</v>
+        <v>1.10696756</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0.0007023713889995342</v>
+        <v>0.0006222208586925682</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>1.294306443477286</v>
+        <v>1.146607733864135</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>1.10071397</v>
+        <v>1.10627921</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0.0004678607164629867</v>
+        <v>0.0009583612225769755</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="43" t="n">
-        <v>0.8621580398234938</v>
+        <v>1.766035924850252</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="41" t="n">
-        <v>1.10019923</v>
+        <v>1.10522001</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0.000801533248670605</v>
+        <v>-0.0003633069101601771</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="43" t="n">
-        <v>1.477038593347847</v>
+        <v>-0.6694897915046658</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B22" s="40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>1.09931809</v>
+        <v>1.10562169</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0.000499240268345913</v>
+        <v>0.0004625329154854807</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="43" t="n">
-        <v>0.9199832258028849</v>
+        <v>0.8523401468358922</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1520,18 +1520,18 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="44" t="inlineStr"/>
       <c r="D25" s="38" t="n">
-        <v>0.01038630184863321</v>
+        <v>0.004570658454711385</v>
       </c>
       <c r="E25" s="38" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F25" s="39" t="n">
-        <v>0.9907409887731735</v>
+        <v>1.201279154087382</v>
       </c>
       <c r="G25" s="45" t="n"/>
     </row>
@@ -1544,13 +1544,13 @@
       </c>
       <c r="C26" s="47" t="inlineStr"/>
       <c r="D26" s="42" t="n">
-        <v>0.0118360103937849</v>
+        <v>0.01237354150256231</v>
       </c>
       <c r="E26" s="42" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F26" s="43" t="n">
-        <v>1.020534428984094</v>
+        <v>1.074986021620339</v>
       </c>
       <c r="G26" s="48" t="n"/>
       <c r="H26" s="49" t="n"/>
@@ -1563,13 +1563,13 @@
       </c>
       <c r="C27" s="47" t="inlineStr"/>
       <c r="D27" s="42" t="n">
-        <v>0.03712118517703122</v>
+        <v>0.03864828806491927</v>
       </c>
       <c r="E27" s="42" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>1.051945144436424</v>
+        <v>1.098004654666819</v>
       </c>
       <c r="G27" s="55" t="n"/>
     </row>
@@ -1582,13 +1582,13 @@
       </c>
       <c r="C28" s="47" t="inlineStr"/>
       <c r="D28" s="42" t="n">
-        <v>0.07404297151655603</v>
+        <v>0.07458524535205457</v>
       </c>
       <c r="E28" s="42" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F28" s="43" t="n">
-        <v>1.030265557652146</v>
+        <v>1.039150536665316</v>
       </c>
       <c r="G28" s="48" t="n"/>
     </row>
@@ -1601,13 +1601,13 @@
       </c>
       <c r="C29" s="47" t="inlineStr"/>
       <c r="D29" s="42" t="n">
-        <v>0.03443351509790671</v>
+        <v>0.04093755351865447</v>
       </c>
       <c r="E29" s="42" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F29" s="43" t="n">
-        <v>1.061484283424162</v>
+        <v>1.075736175059375</v>
       </c>
       <c r="G29" s="48" t="n"/>
     </row>
@@ -1639,13 +1639,13 @@
       </c>
       <c r="C31" s="47" t="inlineStr"/>
       <c r="D31" s="42" t="n">
-        <v>0.1019641899999999</v>
+        <v>0.1088928300000001</v>
       </c>
       <c r="E31" s="42" t="n">
-        <v>0.09214339012094253</v>
+        <v>0.0980845349453765</v>
       </c>
       <c r="F31" s="43" t="n">
-        <v>1.106581707772713</v>
+        <v>1.1101936718224</v>
       </c>
       <c r="G31" s="48" t="n"/>
     </row>
@@ -1673,7 +1673,7 @@
       <c r="C34" s="15" t="n"/>
       <c r="D34" s="15" t="n"/>
       <c r="E34" s="51" t="n">
-        <v>38863132.4</v>
+        <v>41114624.88</v>
       </c>
       <c r="F34" s="30" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -1688,7 +1688,7 @@
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="15" t="n"/>
       <c r="E35" s="51" t="n">
-        <v>27507670.23559006</v>
+        <v>28198446.78327486</v>
       </c>
       <c r="F35" s="30" t="n"/>
       <c r="G35" s="4" t="n"/>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D37" s="21" t="n"/>
